--- a/sources/lei_step4.xlsx
+++ b/sources/lei_step4.xlsx
@@ -785,6 +785,11 @@
           <t>Lei regains 10 points of energy but the throw damage is reduced to 23.</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>915f6ce4-1f16-4f29-88a0-289bf4714220</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>915f6ce4-1f16-4f29-88a0-289bf4714220</t>
@@ -832,6 +837,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1fb94b7c-cb38-4d16-8f0b-b543560350e1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>1fb94b7c-cb38-4d16-8f0b-b543560350e1</t>
@@ -874,6 +884,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>ffe412b1-5618-4c64-9fba-93d447318548</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>ffe412b1-5618-4c64-9fba-93d447318548</t>
@@ -914,6 +929,11 @@
       <c r="L11" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3376e300-d34c-4e03-990c-8cf3dac1403a</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -9613,6 +9633,11 @@
           <t>hhlMmmhmmh</t>
         </is>
       </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>3b08195b-3ba2-4ba2-b20d-f82f3f97efcc</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>3b08195b-3ba2-4ba2-b20d-f82f3f97efcc</t>
@@ -9635,6 +9660,11 @@
           <t>hhlMmmhmLh</t>
         </is>
       </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>ad8ba5a0-00eb-4959-9a6d-1b52886c113e</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>ad8ba5a0-00eb-4959-9a6d-1b52886c113e</t>
@@ -9655,6 +9685,11 @@
       <c r="I199" t="inlineStr">
         <is>
           <t>hhlMMMllm</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>1e9286e9-8453-4085-abd5-d467b2a34a10</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
